--- a/DeskripsiSektor.xlsx
+++ b/DeskripsiSektor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-BETIBEL-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{A976A270-98C2-4F53-806A-7537D1BA3EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4F5000F-5429-4D28-AF5A-E366FE68AF82}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{A976A270-98C2-4F53-806A-7537D1BA3EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CB0DC66-D587-46FD-B7F4-F246AEF19743}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF263468-28F8-4E82-994E-DED788416667}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AF263468-28F8-4E82-994E-DED788416667}"/>
   </bookViews>
   <sheets>
     <sheet name="DeskripsiSektor" sheetId="1" r:id="rId1"/>
@@ -1343,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">

--- a/DeskripsiSektor.xlsx
+++ b/DeskripsiSektor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-BETIBEL-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{A976A270-98C2-4F53-806A-7537D1BA3EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CB0DC66-D587-46FD-B7F4-F246AEF19743}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{A976A270-98C2-4F53-806A-7537D1BA3EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DD4EBB8-1215-4BA0-A0DA-48D2C37866D6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AF263468-28F8-4E82-994E-DED788416667}"/>
   </bookViews>
@@ -961,7 +961,7 @@
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="73.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="59.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
